--- a/PC_2009/AS_026.xlsx
+++ b/PC_2009/AS_026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +40,14 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,8 +60,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -77,11 +101,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,6 +168,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X320"/>
+  <dimension ref="A1:X322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -24517,97 +24600,270 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B320" s="7" t="inlineStr"/>
-      <c r="C320" s="8">
+      <c r="A320" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B320" s="10" t="inlineStr"/>
+      <c r="C320" s="11">
         <f>SUM(C6:C319)</f>
         <v/>
       </c>
-      <c r="D320" s="8">
+      <c r="D320" s="11">
         <f>SUM(D6:D319)</f>
         <v/>
       </c>
-      <c r="E320" s="8">
+      <c r="E320" s="11">
         <f>SUM(E6:E319)</f>
         <v/>
       </c>
-      <c r="F320" s="8">
+      <c r="F320" s="11">
         <f>SUM(F6:F319)</f>
         <v/>
       </c>
-      <c r="G320" s="8">
+      <c r="G320" s="11">
         <f>SUM(G6:G319)</f>
         <v/>
       </c>
-      <c r="H320" s="8">
+      <c r="H320" s="11">
         <f>SUM(H6:H319)</f>
         <v/>
       </c>
-      <c r="I320" s="8">
+      <c r="I320" s="11">
         <f>SUM(I6:I319)</f>
         <v/>
       </c>
-      <c r="J320" s="8">
+      <c r="J320" s="11">
         <f>SUM(J6:J319)</f>
         <v/>
       </c>
-      <c r="K320" s="8">
+      <c r="K320" s="11">
         <f>SUM(K6:K319)</f>
         <v/>
       </c>
-      <c r="L320" s="8">
+      <c r="L320" s="11">
         <f>SUM(L6:L319)</f>
         <v/>
       </c>
-      <c r="M320" s="8">
+      <c r="M320" s="11">
         <f>SUM(M6:M319)</f>
         <v/>
       </c>
-      <c r="N320" s="8">
+      <c r="N320" s="11">
         <f>SUM(N6:N319)</f>
         <v/>
       </c>
-      <c r="O320" s="8">
+      <c r="O320" s="11">
         <f>SUM(O6:O319)</f>
         <v/>
       </c>
-      <c r="P320" s="8">
+      <c r="P320" s="11">
         <f>SUM(P6:P319)</f>
         <v/>
       </c>
-      <c r="Q320" s="8">
+      <c r="Q320" s="11">
         <f>SUM(Q6:Q319)</f>
         <v/>
       </c>
-      <c r="R320" s="8">
+      <c r="R320" s="11">
         <f>SUM(R6:R319)</f>
         <v/>
       </c>
-      <c r="S320" s="8">
+      <c r="S320" s="11">
         <f>SUM(S6:S319)</f>
         <v/>
       </c>
-      <c r="T320" s="8">
+      <c r="T320" s="11">
         <f>SUM(T6:T319)</f>
         <v/>
       </c>
-      <c r="U320" s="8">
+      <c r="U320" s="11">
         <f>SUM(U6:U319)</f>
         <v/>
       </c>
-      <c r="V320" s="8">
+      <c r="V320" s="11">
         <f>SUM(V6:V319)</f>
         <v/>
       </c>
-      <c r="W320" s="8">
+      <c r="W320" s="11">
         <f>SUM(W6:W319)</f>
         <v/>
       </c>
-      <c r="X320" s="7" t="inlineStr"/>
+      <c r="X320" s="11">
+        <f>SUM(X6:X319)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="12" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B321" s="13" t="inlineStr"/>
+      <c r="C321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W321" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X321" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B322" s="16" t="inlineStr"/>
+      <c r="C322" s="17">
+        <f>C320+C321</f>
+        <v/>
+      </c>
+      <c r="D322" s="17">
+        <f>D320+D321</f>
+        <v/>
+      </c>
+      <c r="E322" s="17">
+        <f>E320+E321</f>
+        <v/>
+      </c>
+      <c r="F322" s="17">
+        <f>F320+F321</f>
+        <v/>
+      </c>
+      <c r="G322" s="17">
+        <f>G320+G321</f>
+        <v/>
+      </c>
+      <c r="H322" s="17">
+        <f>H320+H321</f>
+        <v/>
+      </c>
+      <c r="I322" s="17">
+        <f>I320+I321</f>
+        <v/>
+      </c>
+      <c r="J322" s="17">
+        <f>J320+J321</f>
+        <v/>
+      </c>
+      <c r="K322" s="17">
+        <f>K320+K321</f>
+        <v/>
+      </c>
+      <c r="L322" s="17">
+        <f>L320+L321</f>
+        <v/>
+      </c>
+      <c r="M322" s="17">
+        <f>M320+M321</f>
+        <v/>
+      </c>
+      <c r="N322" s="17">
+        <f>N320+N321</f>
+        <v/>
+      </c>
+      <c r="O322" s="17">
+        <f>O320+O321</f>
+        <v/>
+      </c>
+      <c r="P322" s="17">
+        <f>P320+P321</f>
+        <v/>
+      </c>
+      <c r="Q322" s="17">
+        <f>Q320+Q321</f>
+        <v/>
+      </c>
+      <c r="R322" s="17">
+        <f>R320+R321</f>
+        <v/>
+      </c>
+      <c r="S322" s="17">
+        <f>S320+S321</f>
+        <v/>
+      </c>
+      <c r="T322" s="17">
+        <f>T320+T321</f>
+        <v/>
+      </c>
+      <c r="U322" s="17">
+        <f>U320+U321</f>
+        <v/>
+      </c>
+      <c r="V322" s="17">
+        <f>V320+V321</f>
+        <v/>
+      </c>
+      <c r="W322" s="17">
+        <f>W320+W321</f>
+        <v/>
+      </c>
+      <c r="X322" s="17">
+        <f>X320+X321</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PC_2009/AS_026.xlsx
+++ b/PC_2009/AS_026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -79,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -143,11 +148,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,6 +197,23 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -601,7 +631,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -24600,267 +24629,267 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="9" t="inlineStr">
+      <c r="A320" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B320" s="10" t="inlineStr"/>
-      <c r="C320" s="11">
+      <c r="B320" s="19" t="inlineStr"/>
+      <c r="C320" s="20">
         <f>SUM(C6:C319)</f>
         <v/>
       </c>
-      <c r="D320" s="11">
+      <c r="D320" s="20">
         <f>SUM(D6:D319)</f>
         <v/>
       </c>
-      <c r="E320" s="11">
+      <c r="E320" s="20">
         <f>SUM(E6:E319)</f>
         <v/>
       </c>
-      <c r="F320" s="11">
+      <c r="F320" s="20">
         <f>SUM(F6:F319)</f>
         <v/>
       </c>
-      <c r="G320" s="11">
+      <c r="G320" s="20">
         <f>SUM(G6:G319)</f>
         <v/>
       </c>
-      <c r="H320" s="11">
+      <c r="H320" s="20">
         <f>SUM(H6:H319)</f>
         <v/>
       </c>
-      <c r="I320" s="11">
+      <c r="I320" s="20">
         <f>SUM(I6:I319)</f>
         <v/>
       </c>
-      <c r="J320" s="11">
+      <c r="J320" s="20">
         <f>SUM(J6:J319)</f>
         <v/>
       </c>
-      <c r="K320" s="11">
+      <c r="K320" s="20">
         <f>SUM(K6:K319)</f>
         <v/>
       </c>
-      <c r="L320" s="11">
+      <c r="L320" s="20">
         <f>SUM(L6:L319)</f>
         <v/>
       </c>
-      <c r="M320" s="11">
+      <c r="M320" s="20">
         <f>SUM(M6:M319)</f>
         <v/>
       </c>
-      <c r="N320" s="11">
+      <c r="N320" s="20">
         <f>SUM(N6:N319)</f>
         <v/>
       </c>
-      <c r="O320" s="11">
+      <c r="O320" s="20">
         <f>SUM(O6:O319)</f>
         <v/>
       </c>
-      <c r="P320" s="11">
+      <c r="P320" s="20">
         <f>SUM(P6:P319)</f>
         <v/>
       </c>
-      <c r="Q320" s="11">
+      <c r="Q320" s="20">
         <f>SUM(Q6:Q319)</f>
         <v/>
       </c>
-      <c r="R320" s="11">
+      <c r="R320" s="20">
         <f>SUM(R6:R319)</f>
         <v/>
       </c>
-      <c r="S320" s="11">
+      <c r="S320" s="20">
         <f>SUM(S6:S319)</f>
         <v/>
       </c>
-      <c r="T320" s="11">
+      <c r="T320" s="20">
         <f>SUM(T6:T319)</f>
         <v/>
       </c>
-      <c r="U320" s="11">
+      <c r="U320" s="20">
         <f>SUM(U6:U319)</f>
         <v/>
       </c>
-      <c r="V320" s="11">
+      <c r="V320" s="20">
         <f>SUM(V6:V319)</f>
         <v/>
       </c>
-      <c r="W320" s="11">
+      <c r="W320" s="20">
         <f>SUM(W6:W319)</f>
         <v/>
       </c>
-      <c r="X320" s="11">
+      <c r="X320" s="20">
         <f>SUM(X6:X319)</f>
         <v/>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="12" t="inlineStr">
+      <c r="A321" s="21" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B321" s="13" t="inlineStr"/>
-      <c r="C321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W321" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X321" s="14" t="n">
+      <c r="C321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W321" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X321" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="15" t="inlineStr">
+      <c r="A322" s="22" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B322" s="16" t="inlineStr"/>
-      <c r="C322" s="17">
+      <c r="B322" s="23" t="inlineStr"/>
+      <c r="C322" s="24">
         <f>C320+C321</f>
         <v/>
       </c>
-      <c r="D322" s="17">
+      <c r="D322" s="24">
         <f>D320+D321</f>
         <v/>
       </c>
-      <c r="E322" s="17">
+      <c r="E322" s="24">
         <f>E320+E321</f>
         <v/>
       </c>
-      <c r="F322" s="17">
+      <c r="F322" s="24">
         <f>F320+F321</f>
         <v/>
       </c>
-      <c r="G322" s="17">
+      <c r="G322" s="24">
         <f>G320+G321</f>
         <v/>
       </c>
-      <c r="H322" s="17">
+      <c r="H322" s="24">
         <f>H320+H321</f>
         <v/>
       </c>
-      <c r="I322" s="17">
+      <c r="I322" s="24">
         <f>I320+I321</f>
         <v/>
       </c>
-      <c r="J322" s="17">
+      <c r="J322" s="24">
         <f>J320+J321</f>
         <v/>
       </c>
-      <c r="K322" s="17">
+      <c r="K322" s="24">
         <f>K320+K321</f>
         <v/>
       </c>
-      <c r="L322" s="17">
+      <c r="L322" s="24">
         <f>L320+L321</f>
         <v/>
       </c>
-      <c r="M322" s="17">
+      <c r="M322" s="24">
         <f>M320+M321</f>
         <v/>
       </c>
-      <c r="N322" s="17">
+      <c r="N322" s="24">
         <f>N320+N321</f>
         <v/>
       </c>
-      <c r="O322" s="17">
+      <c r="O322" s="24">
         <f>O320+O321</f>
         <v/>
       </c>
-      <c r="P322" s="17">
+      <c r="P322" s="24">
         <f>P320+P321</f>
         <v/>
       </c>
-      <c r="Q322" s="17">
+      <c r="Q322" s="24">
         <f>Q320+Q321</f>
         <v/>
       </c>
-      <c r="R322" s="17">
+      <c r="R322" s="24">
         <f>R320+R321</f>
         <v/>
       </c>
-      <c r="S322" s="17">
+      <c r="S322" s="24">
         <f>S320+S321</f>
         <v/>
       </c>
-      <c r="T322" s="17">
+      <c r="T322" s="24">
         <f>T320+T321</f>
         <v/>
       </c>
-      <c r="U322" s="17">
+      <c r="U322" s="24">
         <f>U320+U321</f>
         <v/>
       </c>
-      <c r="V322" s="17">
+      <c r="V322" s="24">
         <f>V320+V321</f>
         <v/>
       </c>
-      <c r="W322" s="17">
+      <c r="W322" s="24">
         <f>W320+W321</f>
         <v/>
       </c>
-      <c r="X322" s="17">
+      <c r="X322" s="24">
         <f>X320+X321</f>
         <v/>
       </c>
